--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487091_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487091_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.025</v>
+        <v>2.9566</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.1769</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5618</v>
+        <v>3.1335</v>
       </c>
       <c r="G2" t="n">
         <v>2.6853</v>
@@ -610,13 +610,13 @@
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0232</v>
+        <v>0.9548</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1216</v>
+        <v>0.2383</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1448</v>
+        <v>0.7165</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8764999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9207</v>
+        <v>2.773</v>
       </c>
       <c r="E3" t="n">
-        <v>2.187</v>
+        <v>2.1463</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7337</v>
+        <v>0.6267</v>
       </c>
       <c r="G3" t="n">
         <v>2.7192</v>
@@ -688,13 +688,13 @@
         <v>0.386</v>
       </c>
       <c r="S3" t="n">
-        <v>0.078</v>
+        <v>-0.0697</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5037</v>
+        <v>0.463</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4257</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2625</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8109</v>
+        <v>0.3369</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5714</v>
+        <v>-1.313</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3823</v>
+        <v>1.65</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4419</v>
@@ -766,13 +766,13 @@
         <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4151</v>
+        <v>-0.0588</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3194</v>
+        <v>0.5777</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9042</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.06560000000000001</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MARTINEZ FERNANDEZ</t>
+          <t>J. SANCHEZ MARROYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.053</v>
+        <v>-0.1692</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2433</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1903</v>
+        <v>-0.2512</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0193</v>
+        <v>0.2692</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.502</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0907</v>
+        <v>-0.2328</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9144</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.833</v>
+        <v>0.0414</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0814</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9337</v>
+        <v>0.1871</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7616000000000001</v>
+        <v>0.4606</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1721</v>
+        <v>-0.2735</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3511</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3161</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.504</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4785</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3345</v>
+        <v>-0.504</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5717</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8576</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SANCHEZ MARROYO</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1959</v>
+        <v>-0.1999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08210000000000001</v>
+        <v>-1.5041</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.278</v>
+        <v>1.3042</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2692</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.502</v>
+        <v>0.3508</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2328</v>
+        <v>-0.4348</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08210000000000001</v>
+        <v>1.3107</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0414</v>
+        <v>1.9869</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>-0.6762</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1871</v>
+        <v>-1.3948</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4606</v>
+        <v>-1.6361</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2735</v>
+        <v>0.2413</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5308</v>
+        <v>0.2003</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.4263</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5308</v>
+        <v>0.6266</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06560000000000001</v>
+        <v>1.228</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4716</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>S. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.235</v>
+        <v>-0.2007</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3651</v>
+        <v>-0.284</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.6001</v>
+        <v>0.0832</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4258</v>
+        <v>-0.0193</v>
       </c>
       <c r="H7" t="n">
-        <v>1.393</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0328</v>
+        <v>-0.0907</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2358</v>
+        <v>0.9144</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5032</v>
+        <v>0.833</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7326</v>
+        <v>0.0814</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8099</v>
+        <v>-0.9337</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1102</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6998</v>
+        <v>-0.1721</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7371</v>
+        <v>2.3161</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9842</v>
+        <v>-0.9608</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4574</v>
+        <v>-0.5192</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.4416</v>
+        <v>-0.4416</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.4137</v>
+        <v>-0.5717</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3281</v>
+        <v>0.2859</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.0856</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2931</v>
+        <v>-0.3351</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7044</v>
+        <v>4.024</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4113</v>
+        <v>-4.3591</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.08409999999999999</v>
+        <v>1.4258</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3508</v>
+        <v>1.393</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4348</v>
+        <v>0.0328</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3107</v>
+        <v>4.2358</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9869</v>
+        <v>3.5032</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6762</v>
+        <v>0.7326</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3948</v>
+        <v>-2.8099</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6361</v>
+        <v>-2.1102</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2413</v>
+        <v>-0.6998</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3161</v>
+        <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1071</v>
+        <v>-1.0843</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6266</v>
+        <v>0.1164</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7337</v>
+        <v>-1.2007</v>
       </c>
       <c r="V8" t="n">
-        <v>1.228</v>
+        <v>-2.4137</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4716</v>
+        <v>-0.3281</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2436</v>
+        <v>-2.0856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. GARCIA CARRERA</t>
+          <t>E. GANDARILLAS GARMENDIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0434</v>
+        <v>-0.3505</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3274</v>
+        <v>-2.3176</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3709</v>
+        <v>1.9671</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4561</v>
+        <v>0.0284</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8942</v>
+        <v>-0.2536</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5619</v>
+        <v>0.282</v>
       </c>
       <c r="J9" t="n">
-        <v>0.793</v>
+        <v>-0.3994</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5834</v>
+        <v>0.2275</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7904</v>
+        <v>-0.6269</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2491</v>
+        <v>0.4278</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.4775</v>
+        <v>-0.4811</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2285</v>
+        <v>0.9089</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3161</v>
+        <v>0.386</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
         <v>2.3161</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0615</v>
+        <v>-1.1164</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1374</v>
+        <v>-0.2739</v>
       </c>
       <c r="U9" t="n">
-        <v>0.076</v>
+        <v>-0.8425</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.842</v>
+        <v>0.3515</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3281</v>
+        <v>0.2859</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5138</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GANDARILLAS GARMENDIA</t>
+          <t>D. GARCIA CARRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3182</v>
+        <v>-1.3785</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9373</v>
+        <v>0.2868</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6191</v>
+        <v>-1.6653</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0284</v>
+        <v>-1.4561</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2536</v>
+        <v>-0.8942</v>
       </c>
       <c r="I10" t="n">
-        <v>0.282</v>
+        <v>-0.5619</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3994</v>
+        <v>0.793</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2275</v>
+        <v>1.5834</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6269</v>
+        <v>-0.7904</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4278</v>
+        <v>-2.2491</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4811</v>
+        <v>-2.4775</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9089</v>
+        <v>0.2285</v>
       </c>
       <c r="P10" t="n">
-        <v>0.386</v>
+        <v>2.3161</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>2.3161</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0841</v>
+        <v>-0.3966</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-0.1781</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1905</v>
+        <v>-0.2185</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3515</v>
+        <v>-1.842</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2859</v>
+        <v>-0.3281</v>
       </c>
       <c r="X10" t="n">
-        <v>0.06560000000000001</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3397</v>
+        <v>-5.5594</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9291</v>
+        <v>-4.3094</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4105</v>
+        <v>-1.2499</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7215</v>
@@ -1312,13 +1312,13 @@
         <v>2.1231</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4528</v>
+        <v>-0.6725</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1216</v>
+        <v>0.4981</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3313</v>
+        <v>-1.1706</v>
       </c>
       <c r="V11" t="n">
         <v>0.5717</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.721699999999998</v>
+        <v>-2.1268</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.960700000000001</v>
+        <v>-3.3658</v>
       </c>
       <c r="F12" t="n">
-        <v>1.239</v>
+        <v>1.239200000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>1.405</v>
+        <v>1.404999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1343000000000005</v>
+        <v>0.1343000000000014</v>
       </c>
       <c r="I12" t="n">
         <v>1.2709</v>
@@ -1372,10 +1372,10 @@
         <v>-1.1744</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.3041</v>
+        <v>-6.304099999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.7494</v>
+        <v>-8.749400000000001</v>
       </c>
       <c r="O12" t="n">
         <v>2.4453</v>
@@ -1390,19 +1390,19 @@
         <v>16.4057</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.303</v>
+        <v>-3.708</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09879999999999985</v>
+        <v>0.4959999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.2041</v>
+        <v>-4.2042</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.684000000000001</v>
+        <v>-3.684</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9745999999999999</v>
+        <v>0.9746000000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-4.6584</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9864</v>
+        <v>4.3301</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3423</v>
+        <v>2.142</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6441</v>
+        <v>2.1881</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8427</v>
@@ -1468,13 +1468,13 @@
         <v>2.3161</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4456</v>
+        <v>1.7893</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0642</v>
+        <v>0.864</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3814</v>
+        <v>0.9253</v>
       </c>
       <c r="V13" t="n">
         <v>5.1555</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5748</v>
+        <v>2.264</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5217</v>
+        <v>2.3741</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0531</v>
+        <v>-0.1101</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5854</v>
+        <v>2.5985</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7907</v>
+        <v>0.5621</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7947</v>
+        <v>2.0364</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7802</v>
+        <v>3.5262</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9662</v>
+        <v>1.0764</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8139999999999999</v>
+        <v>2.4498</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1948</v>
+        <v>-0.9277</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1755</v>
+        <v>-0.5143</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0193</v>
+        <v>-0.4134</v>
       </c>
       <c r="P14" t="n">
-        <v>1.158</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1231</v>
+        <v>0.772</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4297</v>
+        <v>1.0166</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3471</v>
+        <v>0.971</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0456</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5983</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.6406</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8767</v>
+        <v>2.2281</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1738</v>
+        <v>0.7206</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2972</v>
+        <v>1.5075</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5985</v>
+        <v>1.5854</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5621</v>
+        <v>0.7907</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0364</v>
+        <v>0.7947</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5262</v>
+        <v>2.7802</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0764</v>
+        <v>1.9662</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4498</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9277</v>
+        <v>-1.1948</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5143</v>
+        <v>-1.1755</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4134</v>
+        <v>-0.0193</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>0.772</v>
+        <v>2.1231</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6293</v>
+        <v>1.083</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.546</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1415</v>
+        <v>0.537</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.5983</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-1.6406</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3571</v>
+        <v>1.266</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4293</v>
+        <v>-1.0287</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7864</v>
+        <v>2.2947</v>
       </c>
       <c r="G16" t="n">
         <v>0.6585</v>
@@ -1702,13 +1702,13 @@
         <v>1.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3014</v>
+        <v>0.6075</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4785</v>
+        <v>-0.078</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1771</v>
+        <v>0.6854</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0987</v>
+        <v>0.6804</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5098</v>
+        <v>0.4401</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4111</v>
+        <v>0.2402</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4679</v>
+        <v>1.4619</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0673</v>
+        <v>0.8043</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4006</v>
+        <v>0.6576</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0207</v>
+        <v>1.2148</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0207</v>
+        <v>0.6778</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.537</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4472</v>
+        <v>0.2471</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0466</v>
+        <v>0.1265</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4006</v>
+        <v>0.1207</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0833</v>
+        <v>0.0255</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4891</v>
+        <v>-0.0955</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5724</v>
+        <v>0.1209</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2859</v>
+        <v>-0.614</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0191</v>
+        <v>0.1189</v>
       </c>
       <c r="E18" t="n">
-        <v>0.34</v>
+        <v>0.2094</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3209</v>
+        <v>-0.0905</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4619</v>
+        <v>0.4679</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8043</v>
+        <v>0.0673</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6576</v>
+        <v>0.4006</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2148</v>
+        <v>0.0207</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6778</v>
+        <v>0.0207</v>
       </c>
       <c r="L18" t="n">
-        <v>0.537</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2471</v>
+        <v>0.4472</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1265</v>
+        <v>0.0466</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1207</v>
+        <v>0.4006</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6359</v>
+        <v>-0.0631</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1956</v>
+        <v>0.1887</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4402</v>
+        <v>-0.2518</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.614</v>
+        <v>-0.2859</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8999</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6656</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7232</v>
+        <v>1.1237</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3888</v>
+        <v>-1.2021</v>
       </c>
       <c r="G19" t="n">
         <v>0.7274</v>
@@ -1936,13 +1936,13 @@
         <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3351</v>
+        <v>0.2522</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2062</v>
+        <v>0.6068</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5414</v>
+        <v>-0.3546</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2859</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6969</v>
+        <v>-0.6166</v>
       </c>
       <c r="E20" t="n">
         <v>-0.1966</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5004</v>
+        <v>-0.4201</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2455</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4515</v>
+        <v>-0.3711</v>
       </c>
       <c r="T20" t="n">
         <v>-0.238</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2135</v>
+        <v>-0.1332</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. TAPÉ</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3535</v>
+        <v>-1.0867</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2625</v>
+        <v>-1.091</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.091</v>
+        <v>0.0042</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.095</v>
+        <v>-3.0858</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.095</v>
+        <v>-0.179</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-2.9067</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6676</v>
+        <v>-1.1032</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6676</v>
+        <v>2.1784</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-3.2816</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4274</v>
+        <v>-1.9826</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4274</v>
+        <v>-2.3574</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.3748</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.965</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7066</v>
+        <v>1.0569</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3702</v>
+        <v>0.9496</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3364</v>
+        <v>0.1074</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1857</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>T. TAPÉ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4675</v>
+        <v>-1.6076</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9908</v>
+        <v>-1.4628</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4766</v>
+        <v>-0.1448</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0858</v>
+        <v>-1.095</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.179</v>
+        <v>-1.095</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.9067</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1032</v>
+        <v>-0.6676</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1784</v>
+        <v>-0.6676</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.2816</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9826</v>
+        <v>-0.4274</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3574</v>
+        <v>-0.4274</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3748</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0</v>
+        <v>-0.965</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1231</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6762</v>
+        <v>0.4525</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0497</v>
+        <v>0.1699</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3735</v>
+        <v>0.2826</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1857</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0077</v>
+        <v>-2.1061</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9707</v>
+        <v>-4.47</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9631</v>
+        <v>2.3639</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6358</v>
@@ -2248,13 +2248,13 @@
         <v>2.1231</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2228</v>
+        <v>1.1243</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1811</v>
+        <v>0.3196</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4038</v>
+        <v>0.8047</v>
       </c>
       <c r="V23" t="n">
         <v>0.3704</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.7216</v>
+        <v>5.392199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.239100000000001</v>
+        <v>-1.2392</v>
       </c>
       <c r="F24" t="n">
-        <v>3.960699999999999</v>
+        <v>6.631</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.405199999999999</v>
+        <v>-1.4052</v>
       </c>
       <c r="H24" t="n">
         <v>-0.1340999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>12.5455</v>
       </c>
       <c r="S24" t="n">
-        <v>4.303</v>
+        <v>6.973599999999998</v>
       </c>
       <c r="T24" t="n">
-        <v>4.204</v>
+        <v>4.2041</v>
       </c>
       <c r="U24" t="n">
-        <v>0.09879999999999994</v>
+        <v>2.769299999999999</v>
       </c>
       <c r="V24" t="n">
         <v>3.6839</v>
